--- a/cda_source_dans_fhir/ig/CdaIIToIdentifierConceptMap.xlsx
+++ b/cda_source_dans_fhir/ig/CdaIIToIdentifierConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-01T15:34:26+00:00</t>
+    <t>2026-05-01T15:47:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
